--- a/tasks/finalpool/12306-wc-amazon-product-roadshow-excel-notion/groundtruth_workspace/Roadshow_Plan.xlsx
+++ b/tasks/finalpool/12306-wc-amazon-product-roadshow-excel-notion/groundtruth_workspace/Roadshow_Plan.xlsx
@@ -453,20 +453,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wireless Bluetooth Earbuds Pro</t>
+          <t>NIHARA Wood Smart Multipurpose Foldable Laptop Table with Cup Holder Ergonomic &amp; Rounded Edges (Black)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45.99</v>
+        <v>2.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -474,25 +474,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>820</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Smart Watch Fitness Tracker</t>
+          <t>(Renewed) JBL Flip 4 Portable Wireless Speaker with Powerful Bass &amp; Mic (Squad)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wearables</t>
+          <t>Audio, Speakers</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89.98999999999999</v>
+        <v>86.72</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>650</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USB-C 7-in-1 Hub</t>
+          <t>LIMBANI BROTHERS™ Automatic Vacuum Sealing Machine | Vacuum Sealer for Flatbreads, Nuts, Vegetables, Fruits, Dry-Fruits | ...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Computing Accessories</t>
+          <t>Home Appliances</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.99</v>
+        <v>12.04</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -526,25 +526,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1100</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phone Case with Kickstand</t>
+          <t>Oppo Enco Air 3 True Wireless in-Ear Earbuds with 25hrs Playtime, Fast Charging,13.4mm Driver &amp; BT v5.3 (Glaze White)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mobile Accessories</t>
+          <t>Audio, Headphones</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.99</v>
+        <v>36.13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1450</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adjustable Laptop Stand</t>
+          <t>Oraimo 25.5W 4 Ports USB Charger, 5.1A USB Wall Charger Phone Adapter Compatible for iPhone 13/13 Mini/13 Pro Max/12/12 Pr...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Computing Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49.99</v>
+        <v>7.22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>580</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
